--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Introudction in Pyhton EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\RIDERORMAX\Introudction in Pyhton EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -207,6 +207,18 @@
   </si>
   <si>
     <t>August</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Tired after classes and my legs hurt. Feel better after a campus walk. Low energy, but I still need to study.</t>
   </si>
 </sst>
 </file>
@@ -1032,27 +1044,51 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+    <row r="7" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="13">
+        <v>46215</v>
+      </c>
+      <c r="B7" s="14">
+        <v>330</v>
+      </c>
+      <c r="C7" s="14">
+        <v>150</v>
+      </c>
+      <c r="D7" s="14">
+        <v>90</v>
+      </c>
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
+        <v>350</v>
+      </c>
+      <c r="G7" s="14">
+        <v>7</v>
+      </c>
+      <c r="H7" s="14">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>Tired after classes and my legs hurt. Feel better after a campus walk. Low energy, but I still need to study.</t>
+  </si>
+  <si>
+    <t>Doing repeated classes but after final class I go for Elachi tea and campus walk from Cricket Ground to LPU Main Gate</t>
   </si>
 </sst>
 </file>
@@ -1090,27 +1093,51 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="8" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
+        <v>46216</v>
+      </c>
+      <c r="B8" s="14">
+        <v>240</v>
+      </c>
+      <c r="C8" s="14">
+        <v>170</v>
+      </c>
+      <c r="D8" s="14">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14">
+        <v>400</v>
+      </c>
+      <c r="G8" s="14">
+        <v>8</v>
+      </c>
+      <c r="H8" s="14">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -222,6 +222,18 @@
   </si>
   <si>
     <t>Doing repeated classes but after final class I go for Elachi tea and campus walk from Cricket Ground to LPU Main Gate</t>
+  </si>
+  <si>
+    <t>Sir gave us three C++ questions in class, and I solved tem correctly. After solving questions, I felt really good and satisfied.</t>
+  </si>
+  <si>
+    <t>Holiday (Happy Independence Day)</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Today, my time mostly to wash my all dirty clothes which takes a lot of time and making my wardrobe.</t>
   </si>
 </sst>
 </file>
@@ -1139,49 +1151,97 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="13">
+        <v>46217</v>
+      </c>
+      <c r="B9" s="14">
+        <v>240</v>
+      </c>
+      <c r="C9" s="14">
+        <v>180</v>
+      </c>
+      <c r="D9" s="14">
+        <v>100</v>
+      </c>
+      <c r="E9" s="14">
+        <v>50</v>
+      </c>
+      <c r="F9" s="14">
+        <v>300</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+      <c r="H9" s="14">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="13">
+        <v>46218</v>
+      </c>
+      <c r="B10" s="14">
+        <v>360</v>
+      </c>
+      <c r="C10" s="14">
+        <v>60</v>
+      </c>
+      <c r="D10" s="14">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="14">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>1020</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -234,6 +234,12 @@
   </si>
   <si>
     <t>Today, my time mostly to wash my all dirty clothes which takes a lot of time and making my wardrobe.</t>
+  </si>
+  <si>
+    <t>No Class/Holiday</t>
+  </si>
+  <si>
+    <t>I was out on campus for the entire day to purchase some essential items, which took quite a lot of time. I ca  manage walking around for the whole day, but once I took the rest, I started  experiencing pain in my legs and felt quite tired. As a result, I went to bed early.</t>
   </si>
 </sst>
 </file>
@@ -1243,27 +1249,51 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+    <row r="11" spans="1:14" ht="150" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>46219</v>
+      </c>
+      <c r="B11" s="14">
+        <v>360</v>
+      </c>
+      <c r="C11" s="14">
+        <v>60</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="14">
+        <v>255</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>675</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>765</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
@@ -1274,14 +1304,8 @@
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
       <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
       <c r="K12" s="16"/>
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>I was out on campus for the entire day to purchase some essential items, which took quite a lot of time. I ca  manage walking around for the whole day, but once I took the rest, I started  experiencing pain in my legs and felt quite tired. As a result, I went to bed early.</t>
+  </si>
+  <si>
+    <t>Try to understand the Data Communication and Networking subjects which is taught by the professor and try to revise it.</t>
   </si>
 </sst>
 </file>
@@ -1295,21 +1298,51 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+    <row r="12" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="13">
+        <v>46220</v>
+      </c>
+      <c r="B12" s="14">
+        <v>450</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="1"/>
+        <v>810</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>Try to understand the Data Communication and Networking subjects which is taught by the professor and try to revise it.</t>
+  </si>
+  <si>
+    <t>Today, I revise the things which was taught by our professor and also done some practices and I feel little happy I am slowly reeducing my free minute into a productive min</t>
   </si>
 </sst>
 </file>
@@ -1344,27 +1347,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+    <row r="13" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+      <c r="A13" s="13">
+        <v>46221</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>240</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -246,6 +246,15 @@
   </si>
   <si>
     <t>Today, I revise the things which was taught by our professor and also done some practices and I feel little happy I am slowly reeducing my free minute into a productive min</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Feel productive day because I practice some networking questions and try to understand SQL commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revising C++ and Database </t>
   </si>
 </sst>
 </file>
@@ -1393,49 +1402,97 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="13">
+        <v>46222</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46223</v>
+      </c>
+      <c r="B15" s="14">
+        <v>450</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>180</v>
+      </c>
+      <c r="E15" s="14">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
